--- a/inputs/input_data_intertemporal_final.xlsx
+++ b/inputs/input_data_intertemporal_final.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DDC7A8-A682-4655-AB83-8BDEFD26A2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE06F6B7-0C9E-4815-AD0C-74F82045695E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
-    <sheet name="regions" sheetId="4" r:id="rId2"/>
+    <sheet name="regions" sheetId="2" r:id="rId2"/>
     <sheet name="params_region" sheetId="3" r:id="rId3"/>
-    <sheet name="c_ship" sheetId="2" r:id="rId4"/>
+    <sheet name="c_ship" sheetId="4" r:id="rId4"/>
     <sheet name="README" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -38,6 +38,9 @@
     <t>players</t>
   </si>
   <si>
+    <t>ch,eu,us,apac,roa,af,row</t>
+  </si>
+  <si>
     <t>damping_eta</t>
   </si>
   <si>
@@ -59,106 +62,106 @@
     <t>scenario_capitalistic_china</t>
   </si>
   <si>
-    <t>ch,eu,us,apac,roa,af,row</t>
+    <t>r</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>ch</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>eu</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>North America</t>
+  </si>
+  <si>
+    <t>apac</t>
+  </si>
+  <si>
+    <t>Asia Pacific</t>
+  </si>
+  <si>
+    <t>roa</t>
+  </si>
+  <si>
+    <t>Rest of Asia</t>
+  </si>
+  <si>
+    <t>af</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>row</t>
+  </si>
+  <si>
+    <t>Rest of World</t>
+  </si>
+  <si>
+    <t>Qcap_exist (GW)</t>
+  </si>
+  <si>
+    <t>Dmax_2025 (GW)</t>
+  </si>
+  <si>
+    <t>Dmax_2030 (GW)</t>
+  </si>
+  <si>
+    <t>Dmax_2035(GW)</t>
+  </si>
+  <si>
+    <t>Dmax_2040 (GW)</t>
+  </si>
+  <si>
+    <t>c_man (USD/kW)</t>
+  </si>
+  <si>
+    <t>a_dem (USD/kW)</t>
+  </si>
+  <si>
+    <t>b_dem (USD/kW)</t>
+  </si>
+  <si>
+    <t>c_inv (mUSD/GW-yr)</t>
+  </si>
+  <si>
+    <t>f_hold (mUSD/GW-yr)</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>Kcap_2025 (GW)</t>
+  </si>
+  <si>
+    <t>g_exp_ub (rate/yr)</t>
+  </si>
+  <si>
+    <t>g_dec_ub (rate/yr)</t>
+  </si>
+  <si>
+    <t>p_offer_max (USD/kW)</t>
+  </si>
+  <si>
+    <t>rho_p (scalar)</t>
+  </si>
+  <si>
+    <t>c_inv = Annualized Integrated CapEx (20 yr). f_hold = Fixed O&amp;M (~2% CapEx).</t>
   </si>
   <si>
     <t>exporter</t>
-  </si>
-  <si>
-    <t>ch</t>
-  </si>
-  <si>
-    <t>eu</t>
-  </si>
-  <si>
-    <t>us</t>
-  </si>
-  <si>
-    <t>apac</t>
-  </si>
-  <si>
-    <t>roa</t>
-  </si>
-  <si>
-    <t>af</t>
-  </si>
-  <si>
-    <t>row</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>Qcap_exist (GW)</t>
-  </si>
-  <si>
-    <t>Dmax_2025 (GW)</t>
-  </si>
-  <si>
-    <t>Dmax_2030 (GW)</t>
-  </si>
-  <si>
-    <t>Dmax_2035(GW)</t>
-  </si>
-  <si>
-    <t>Dmax_2040 (GW)</t>
-  </si>
-  <si>
-    <t>c_man (USD/kW)</t>
-  </si>
-  <si>
-    <t>a_dem (USD/kW)</t>
-  </si>
-  <si>
-    <t>c_inv (mUSD/GW-yr)</t>
-  </si>
-  <si>
-    <t>f_hold (mUSD/GW-yr)</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>Kcap_2025 (GW)</t>
-  </si>
-  <si>
-    <t>g_exp_ub (rate/yr)</t>
-  </si>
-  <si>
-    <t>g_dec_ub (rate/yr)</t>
-  </si>
-  <si>
-    <t>p_offer_max (USD/kW)</t>
-  </si>
-  <si>
-    <t>rho_p (penalty weight)</t>
-  </si>
-  <si>
-    <t>c_inv = Annualized Integrated CapEx (20 yr). f_hold = Fixed O&amp;M (~2% CapEx).</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>China</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>North America</t>
-  </si>
-  <si>
-    <t>Asia Pacific</t>
-  </si>
-  <si>
-    <t>Rest of Asia</t>
-  </si>
-  <si>
-    <t>Africa</t>
-  </si>
-  <si>
-    <t>Rest of World</t>
   </si>
   <si>
     <t>README</t>
@@ -171,9 +174,6 @@
 Color convention:
 Blue = editable inputs; Black = derived/formulas
 </t>
-  </si>
-  <si>
-    <t>b_dem (USD/kW)</t>
   </si>
 </sst>
 </file>
@@ -562,42 +562,42 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -606,72 +606,72 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -704,60 +704,60 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>931</v>
@@ -790,7 +790,7 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M2">
         <v>20</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>22</v>
@@ -843,7 +843,7 @@
         <v>8.5</v>
       </c>
       <c r="L3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M3">
         <v>20</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>23</v>
@@ -896,7 +896,7 @@
         <v>7.5</v>
       </c>
       <c r="L4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M4">
         <v>20</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>110</v>
@@ -949,7 +949,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M5">
         <v>20</v>
@@ -969,7 +969,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1002,7 +1002,7 @@
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M6">
         <v>20</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>3.4</v>
@@ -1055,7 +1055,7 @@
         <v>9</v>
       </c>
       <c r="L7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M7">
         <v>20</v>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>293</v>
@@ -1108,7 +1108,7 @@
         <v>9</v>
       </c>
       <c r="L8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M8">
         <v>20</v>
@@ -1132,39 +1132,39 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>16.117999999999999</v>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>24.731000000000002</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>12.40564545454545</v>
@@ -1268,7 +1268,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>14.082000000000001</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>4.5</v>
@@ -1320,7 +1320,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>14.122395904436861</v>
@@ -1356,12 +1356,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/input_data_intertemporal_final.xlsx
+++ b/inputs/input_data_intertemporal_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE06F6B7-0C9E-4815-AD0C-74F82045695E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3E6695-A37F-4999-9DD5-431FF481FD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
   <si>
     <t>setting</t>
   </si>
@@ -156,6 +156,30 @@
   </si>
   <si>
     <t>rho_p (scalar)</t>
+  </si>
+  <si>
+    <t>a_dem_2025</t>
+  </si>
+  <si>
+    <t>a_dem_2030</t>
+  </si>
+  <si>
+    <t>a_dem_2035</t>
+  </si>
+  <si>
+    <t>a_dem_2040</t>
+  </si>
+  <si>
+    <t>b_dem_2025</t>
+  </si>
+  <si>
+    <t>b_dem_2030</t>
+  </si>
+  <si>
+    <t>b_dem_2035</t>
+  </si>
+  <si>
+    <t>b_dem_2040</t>
   </si>
   <si>
     <t>c_inv = Annualized Integrated CapEx (20 yr). f_hold = Fixed O&amp;M (~2% CapEx).</t>
@@ -180,7 +204,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,6 +220,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -205,7 +234,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -228,13 +257,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -681,81 +728,101 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="31.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="23.140625" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" customWidth="1"/>
-    <col min="9" max="9" width="30.140625" customWidth="1"/>
-    <col min="10" max="10" width="33" customWidth="1"/>
-    <col min="11" max="11" width="31.28515625" customWidth="1"/>
-    <col min="12" max="12" width="19.85546875" customWidth="1"/>
-    <col min="13" max="13" width="17.42578125" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
-    <col min="16" max="16" width="24" customWidth="1"/>
-    <col min="17" max="17" width="34.42578125" customWidth="1"/>
+    <col min="14" max="14" width="17.140625" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" customWidth="1"/>
+    <col min="16" max="16" width="20.28515625" customWidth="1"/>
+    <col min="17" max="17" width="22.140625" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="15.7109375" customWidth="1"/>
+    <col min="21" max="21" width="15" customWidth="1"/>
+    <col min="22" max="22" width="17.28515625" customWidth="1"/>
+    <col min="23" max="23" width="16.85546875" customWidth="1"/>
+    <col min="24" max="24" width="17.7109375" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -790,7 +857,7 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M2">
         <v>20</v>
@@ -807,8 +874,32 @@
       <c r="Q2">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R2">
+        <v>400</v>
+      </c>
+      <c r="S2">
+        <v>400</v>
+      </c>
+      <c r="T2">
+        <v>400</v>
+      </c>
+      <c r="U2">
+        <v>400</v>
+      </c>
+      <c r="V2">
+        <v>1.0069999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="X2">
+        <v>0.51900000000000002</v>
+      </c>
+      <c r="Y2">
+        <v>0.46700000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -843,7 +934,7 @@
         <v>8.5</v>
       </c>
       <c r="L3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M3">
         <v>20</v>
@@ -860,8 +951,32 @@
       <c r="Q3">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R3">
+        <v>450</v>
+      </c>
+      <c r="S3">
+        <v>450</v>
+      </c>
+      <c r="T3">
+        <v>450</v>
+      </c>
+      <c r="U3">
+        <v>450</v>
+      </c>
+      <c r="V3">
+        <v>5.5940000000000003</v>
+      </c>
+      <c r="W3">
+        <v>4.8529999999999998</v>
+      </c>
+      <c r="X3">
+        <v>2.2759999999999998</v>
+      </c>
+      <c r="Y3">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -896,7 +1011,7 @@
         <v>7.5</v>
       </c>
       <c r="L4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M4">
         <v>20</v>
@@ -913,8 +1028,32 @@
       <c r="Q4">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R4">
+        <v>500</v>
+      </c>
+      <c r="S4">
+        <v>500</v>
+      </c>
+      <c r="T4">
+        <v>500</v>
+      </c>
+      <c r="U4">
+        <v>500</v>
+      </c>
+      <c r="V4">
+        <v>9.93</v>
+      </c>
+      <c r="W4">
+        <v>5.4290000000000003</v>
+      </c>
+      <c r="X4">
+        <v>4</v>
+      </c>
+      <c r="Y4">
+        <v>3.3039999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -949,7 +1088,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="L5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M5">
         <v>20</v>
@@ -966,8 +1105,32 @@
       <c r="Q5">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R5">
+        <v>400</v>
+      </c>
+      <c r="S5">
+        <v>400</v>
+      </c>
+      <c r="T5">
+        <v>400</v>
+      </c>
+      <c r="U5">
+        <v>400</v>
+      </c>
+      <c r="V5">
+        <v>4.3109999999999999</v>
+      </c>
+      <c r="W5">
+        <v>2.8</v>
+      </c>
+      <c r="X5">
+        <v>1.806</v>
+      </c>
+      <c r="Y5">
+        <v>1.333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1002,7 +1165,7 @@
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M6">
         <v>20</v>
@@ -1019,8 +1182,32 @@
       <c r="Q6">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R6">
+        <v>400</v>
+      </c>
+      <c r="S6">
+        <v>400</v>
+      </c>
+      <c r="T6">
+        <v>400</v>
+      </c>
+      <c r="U6">
+        <v>400</v>
+      </c>
+      <c r="V6">
+        <v>19.113</v>
+      </c>
+      <c r="W6">
+        <v>14</v>
+      </c>
+      <c r="X6">
+        <v>6.2220000000000004</v>
+      </c>
+      <c r="Y6">
+        <v>3.7330000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1055,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="L7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M7">
         <v>20</v>
@@ -1072,8 +1259,32 @@
       <c r="Q7">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R7">
+        <v>350</v>
+      </c>
+      <c r="S7">
+        <v>350</v>
+      </c>
+      <c r="T7">
+        <v>350</v>
+      </c>
+      <c r="U7">
+        <v>350</v>
+      </c>
+      <c r="V7">
+        <v>60.209000000000003</v>
+      </c>
+      <c r="W7">
+        <v>32.856999999999999</v>
+      </c>
+      <c r="X7">
+        <v>15.333</v>
+      </c>
+      <c r="Y7">
+        <v>7.6669999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1108,7 +1319,7 @@
         <v>9</v>
       </c>
       <c r="L8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M8">
         <v>20</v>
@@ -1125,9 +1336,33 @@
       <c r="Q8">
         <v>1E-3</v>
       </c>
+      <c r="R8">
+        <v>400</v>
+      </c>
+      <c r="S8">
+        <v>400</v>
+      </c>
+      <c r="T8">
+        <v>400</v>
+      </c>
+      <c r="U8">
+        <v>400</v>
+      </c>
+      <c r="V8">
+        <v>8.3089999999999993</v>
+      </c>
+      <c r="W8">
+        <v>5.6</v>
+      </c>
+      <c r="X8">
+        <v>3.1110000000000002</v>
+      </c>
+      <c r="Y8">
+        <v>2.1539999999999999</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1138,7 +1373,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>14</v>
@@ -1356,12 +1591,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/input_data_intertemporal_final.xlsx
+++ b/inputs/input_data_intertemporal_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3E6695-A37F-4999-9DD5-431FF481FD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EDA1B2-A814-4494-9F17-4AD566B6C8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6300" yWindow="1890" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -731,6 +731,11 @@
   <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
     <col min="14" max="14" width="17.140625" customWidth="1"/>
     <col min="15" max="15" width="17.5703125" customWidth="1"/>
     <col min="16" max="16" width="20.28515625" customWidth="1"/>
@@ -869,7 +874,7 @@
         <v>0.5</v>
       </c>
       <c r="P2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q2">
         <v>1E-3</v>
@@ -946,7 +951,7 @@
         <v>0.5</v>
       </c>
       <c r="P3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>1E-3</v>
@@ -1023,7 +1028,7 @@
         <v>0.5</v>
       </c>
       <c r="P4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <v>1E-3</v>
@@ -1100,7 +1105,7 @@
         <v>0.5</v>
       </c>
       <c r="P5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>1E-3</v>
@@ -1177,7 +1182,7 @@
         <v>0.5</v>
       </c>
       <c r="P6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>1E-3</v>
@@ -1254,7 +1259,7 @@
         <v>0.5</v>
       </c>
       <c r="P7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>1E-3</v>
@@ -1331,7 +1336,7 @@
         <v>0.5</v>
       </c>
       <c r="P8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <v>1E-3</v>

--- a/inputs/input_data_intertemporal_final.xlsx
+++ b/inputs/input_data_intertemporal_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EEG\EPEC\EPEC_VS_code\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EDA1B2-A814-4494-9F17-4AD566B6C8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF84FCA-830E-43AF-B02A-5EA1FEFBD53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6300" yWindow="1890" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-930" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,25 @@
     <sheet name="c_ship" sheetId="4" r:id="rId4"/>
     <sheet name="README" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="57">
   <si>
     <t>setting</t>
   </si>
@@ -38,7 +51,7 @@
     <t>players</t>
   </si>
   <si>
-    <t>ch,eu,us,apac,roa,af,row</t>
+    <t>ch,eu,us,apac,af,row</t>
   </si>
   <si>
     <t>damping_eta</t>
@@ -89,13 +102,7 @@
     <t>apac</t>
   </si>
   <si>
-    <t>Asia Pacific</t>
-  </si>
-  <si>
-    <t>roa</t>
-  </si>
-  <si>
-    <t>Rest of Asia</t>
+    <t>Asia (APAC+ROA)</t>
   </si>
   <si>
     <t>af</t>
@@ -128,12 +135,6 @@
     <t>c_man (USD/kW)</t>
   </si>
   <si>
-    <t>a_dem (USD/kW)</t>
-  </si>
-  <si>
-    <t>b_dem (USD/kW)</t>
-  </si>
-  <si>
     <t>c_inv (mUSD/GW-yr)</t>
   </si>
   <si>
@@ -183,6 +184,9 @@
   </si>
   <si>
     <t>c_inv = Annualized Integrated CapEx (20 yr). f_hold = Fixed O&amp;M (~2% CapEx).</t>
+  </si>
+  <si>
+    <t>Merged APAC+ROA on 2026-03-02: Dmax/Qcap summed; c_man,c_inv,f_hold demand-weighted by Dmax_2025; b_dem combined via 1/b=1/b1+1/b2.</t>
   </si>
   <si>
     <t>exporter</t>
@@ -199,12 +203,24 @@
 Blue = editable inputs; Black = derived/formulas
 </t>
   </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>china</t>
+  </si>
+  <si>
+    <t>estimated WTP for full demand</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -225,6 +241,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -234,7 +256,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -272,11 +294,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -284,9 +386,57 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -589,9 +739,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -599,12 +749,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -612,37 +762,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -654,10 +804,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -665,7 +815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -673,7 +823,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -681,7 +831,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -689,7 +839,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -697,7 +847,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -705,20 +855,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -728,106 +870,105 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Y8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:W58"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7265625" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="17.140625" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" customWidth="1"/>
-    <col min="16" max="16" width="20.28515625" customWidth="1"/>
-    <col min="17" max="17" width="22.140625" customWidth="1"/>
-    <col min="18" max="18" width="20" customWidth="1"/>
-    <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="15.7109375" customWidth="1"/>
-    <col min="21" max="21" width="15" customWidth="1"/>
-    <col min="22" max="22" width="17.28515625" customWidth="1"/>
-    <col min="23" max="23" width="16.85546875" customWidth="1"/>
-    <col min="24" max="24" width="17.7109375" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" customWidth="1"/>
+    <col min="8" max="8" width="24.90625" customWidth="1"/>
+    <col min="9" max="9" width="20.54296875" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="18.36328125" customWidth="1"/>
+    <col min="12" max="12" width="17.1796875" customWidth="1"/>
+    <col min="13" max="13" width="17.54296875" customWidth="1"/>
+    <col min="14" max="14" width="20.26953125" customWidth="1"/>
+    <col min="15" max="15" width="22.1796875" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="15.7265625" customWidth="1"/>
+    <col min="19" max="19" width="15" customWidth="1"/>
+    <col min="20" max="20" width="17.26953125" customWidth="1"/>
+    <col min="21" max="21" width="16.81640625" customWidth="1"/>
+    <col min="22" max="22" width="17.7265625" customWidth="1"/>
+    <col min="23" max="23" width="20.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="U1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="V1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="W1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="V1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -850,61 +991,55 @@
         <v>163</v>
       </c>
       <c r="H2">
-        <v>463</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1.079137</v>
-      </c>
-      <c r="J2">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="J2" t="s">
+        <v>48</v>
       </c>
       <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2" t="s">
-        <v>52</v>
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>0.5</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="N2">
-        <v>0.5</v>
+        <v>1000</v>
       </c>
       <c r="O2">
-        <v>0.5</v>
+        <v>1E-3</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>521.41999999999996</v>
       </c>
       <c r="Q2">
-        <v>1E-3</v>
+        <v>500</v>
       </c>
       <c r="R2">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S2">
-        <v>400</v>
-      </c>
-      <c r="T2">
-        <v>400</v>
-      </c>
-      <c r="U2">
-        <v>400</v>
-      </c>
-      <c r="V2">
-        <v>1.0069999999999999</v>
-      </c>
-      <c r="W2">
-        <v>0.68300000000000005</v>
-      </c>
-      <c r="X2">
-        <v>0.51900000000000002</v>
-      </c>
-      <c r="Y2">
-        <v>0.46700000000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+      <c r="T2" s="5">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="V2" s="5">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="W2" s="5">
+        <v>0.309</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -927,61 +1062,55 @@
         <v>299.25</v>
       </c>
       <c r="H3">
-        <v>699.25</v>
+        <v>21.25</v>
       </c>
       <c r="I3">
-        <v>6.7808099999999998</v>
-      </c>
-      <c r="J3">
-        <v>21.25</v>
+        <v>8.5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>48</v>
       </c>
       <c r="K3">
-        <v>8.5</v>
-      </c>
-      <c r="L3" t="s">
-        <v>52</v>
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>0.5</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="N3">
-        <v>0.5</v>
+        <v>1000</v>
       </c>
       <c r="O3">
-        <v>0.5</v>
+        <v>1E-3</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q3">
-        <v>1E-3</v>
+        <v>500</v>
       </c>
       <c r="R3">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="S3">
-        <v>450</v>
-      </c>
-      <c r="T3">
-        <v>450</v>
-      </c>
-      <c r="U3">
-        <v>450</v>
-      </c>
-      <c r="V3">
-        <v>5.5940000000000003</v>
-      </c>
-      <c r="W3">
-        <v>4.8529999999999998</v>
-      </c>
-      <c r="X3">
-        <v>2.2759999999999998</v>
-      </c>
-      <c r="Y3">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+      <c r="T3" s="5">
+        <v>3.141</v>
+      </c>
+      <c r="U3" s="5">
+        <v>2.7240000000000002</v>
+      </c>
+      <c r="V3" s="5">
+        <v>1.2769999999999999</v>
+      </c>
+      <c r="W3" s="5">
+        <v>0.74099999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1004,34 +1133,34 @@
         <v>321.25</v>
       </c>
       <c r="H4">
-        <v>521.25</v>
+        <v>18.75</v>
       </c>
       <c r="I4">
-        <v>5.2267080000000004</v>
-      </c>
-      <c r="J4">
-        <v>18.75</v>
+        <v>7.5</v>
+      </c>
+      <c r="J4" t="s">
+        <v>48</v>
       </c>
       <c r="K4">
-        <v>7.5</v>
-      </c>
-      <c r="L4" t="s">
-        <v>52</v>
+        <v>20</v>
+      </c>
+      <c r="L4">
+        <v>0.5</v>
       </c>
       <c r="M4">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="N4">
-        <v>0.5</v>
+        <v>1000</v>
       </c>
       <c r="O4">
-        <v>0.5</v>
+        <v>1E-3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q4">
-        <v>1E-3</v>
+        <v>500</v>
       </c>
       <c r="R4">
         <v>500</v>
@@ -1039,26 +1168,20 @@
       <c r="S4">
         <v>500</v>
       </c>
-      <c r="T4">
-        <v>500</v>
-      </c>
-      <c r="U4">
-        <v>500</v>
-      </c>
-      <c r="V4">
-        <v>9.93</v>
-      </c>
-      <c r="W4">
-        <v>5.4290000000000003</v>
-      </c>
-      <c r="X4">
-        <v>4</v>
-      </c>
-      <c r="Y4">
-        <v>3.3039999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="T4" s="5">
+        <v>4.8390000000000004</v>
+      </c>
+      <c r="U4" s="5">
+        <v>2.6459999999999999</v>
+      </c>
+      <c r="V4" s="5">
+        <v>1.9490000000000001</v>
+      </c>
+      <c r="W4" s="5">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1066,343 +1189,712 @@
         <v>110</v>
       </c>
       <c r="C5">
-        <v>24.86</v>
+        <v>49.08</v>
       </c>
       <c r="D5">
-        <v>47.86</v>
+        <v>290</v>
       </c>
       <c r="E5">
-        <v>65</v>
+        <v>375</v>
       </c>
       <c r="F5">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="G5">
-        <v>180.38</v>
+        <v>265.75204563977178</v>
       </c>
       <c r="H5">
-        <v>429.9520098205291</v>
+        <v>11.74022004889976</v>
       </c>
       <c r="I5">
-        <v>9.9676984296108451</v>
-      </c>
-      <c r="J5">
-        <v>11</v>
+        <v>4.6960880195599017</v>
+      </c>
+      <c r="J5" t="s">
+        <v>49</v>
       </c>
       <c r="K5">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L5" t="s">
-        <v>52</v>
+        <v>20</v>
+      </c>
+      <c r="L5">
+        <v>0.5</v>
       </c>
       <c r="M5">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="N5">
-        <v>0.5</v>
+        <v>1000</v>
       </c>
       <c r="O5">
-        <v>0.5</v>
+        <v>1E-3</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q5">
-        <v>1E-3</v>
+        <v>500</v>
       </c>
       <c r="R5">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S5">
-        <v>400</v>
-      </c>
-      <c r="T5">
-        <v>400</v>
-      </c>
-      <c r="U5">
-        <v>400</v>
-      </c>
-      <c r="V5">
-        <v>4.3109999999999999</v>
-      </c>
-      <c r="W5">
-        <v>2.8</v>
-      </c>
-      <c r="X5">
-        <v>1.806</v>
-      </c>
-      <c r="Y5">
-        <v>1.333</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+      <c r="T5" s="5">
+        <v>3.77408106497119</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0.63868335851500102</v>
+      </c>
+      <c r="V5" s="5">
+        <v>0.48424802277760198</v>
+      </c>
+      <c r="W5" s="5">
+        <v>0.40235724482512492</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="C6">
-        <v>24.22</v>
+        <v>18.2</v>
       </c>
       <c r="D6">
-        <v>242.14</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>310</v>
+        <v>62</v>
       </c>
       <c r="F6">
-        <v>380</v>
+        <v>90</v>
       </c>
       <c r="G6">
-        <v>353.38</v>
+        <v>180.93</v>
       </c>
       <c r="H6">
-        <v>553.375</v>
+        <v>22.5</v>
       </c>
       <c r="I6">
-        <v>8.257638</v>
-      </c>
-      <c r="J6">
-        <v>12.5</v>
+        <v>9</v>
+      </c>
+      <c r="J6" t="s">
+        <v>48</v>
       </c>
       <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6" t="s">
-        <v>52</v>
+        <v>20</v>
+      </c>
+      <c r="L6">
+        <v>0.5</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="N6">
-        <v>0.5</v>
+        <v>1000</v>
       </c>
       <c r="O6">
-        <v>0.5</v>
+        <v>1E-3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Q6">
-        <v>1E-3</v>
+        <v>500</v>
       </c>
       <c r="R6">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S6">
-        <v>400</v>
-      </c>
-      <c r="T6">
-        <v>400</v>
-      </c>
-      <c r="U6">
-        <v>400</v>
-      </c>
-      <c r="V6">
-        <v>19.113</v>
-      </c>
-      <c r="W6">
-        <v>14</v>
-      </c>
-      <c r="X6">
-        <v>6.2220000000000004</v>
-      </c>
-      <c r="Y6">
-        <v>3.7330000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+      <c r="T6" s="5">
+        <v>10.177</v>
+      </c>
+      <c r="U6" s="5">
+        <v>5.6120000000000001</v>
+      </c>
+      <c r="V6" s="5">
+        <v>2.9870000000000001</v>
+      </c>
+      <c r="W6" s="5">
+        <v>2.0579999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>3.4</v>
+        <v>293</v>
       </c>
       <c r="C7">
-        <v>18.2</v>
+        <v>27.61</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>90.56</v>
       </c>
       <c r="E7">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="F7">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G7">
-        <v>180.93</v>
+        <v>353.38</v>
       </c>
       <c r="H7">
-        <v>553.375</v>
+        <v>22.5</v>
       </c>
       <c r="I7">
-        <v>7.2441750000000003</v>
-      </c>
-      <c r="J7">
-        <v>22.5</v>
+        <v>9</v>
+      </c>
+      <c r="J7" t="s">
+        <v>48</v>
       </c>
       <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7" t="s">
-        <v>52</v>
+        <v>20</v>
+      </c>
+      <c r="L7">
+        <v>0.5</v>
       </c>
       <c r="M7">
+        <v>0.5</v>
+      </c>
+      <c r="N7">
+        <v>1000</v>
+      </c>
+      <c r="O7">
+        <v>1E-3</v>
+      </c>
+      <c r="P7">
+        <v>500</v>
+      </c>
+      <c r="Q7">
+        <v>500</v>
+      </c>
+      <c r="R7">
+        <v>500</v>
+      </c>
+      <c r="S7">
+        <v>500</v>
+      </c>
+      <c r="T7" s="5">
+        <v>6.7110000000000003</v>
+      </c>
+      <c r="U7" s="5">
+        <v>2.0449999999999999</v>
+      </c>
+      <c r="V7" s="5">
+        <v>1.425</v>
+      </c>
+      <c r="W7" s="5">
+        <v>1.026</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+    </row>
+    <row r="13" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="8">
+        <v>521.41999999999996</v>
+      </c>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B15" s="13">
+        <v>2025</v>
+      </c>
+      <c r="C15" s="14">
+        <f>C2+0.5*$P$2</f>
+        <v>538.71</v>
+      </c>
+      <c r="D15" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="B16" s="13">
+        <v>2030</v>
+      </c>
+      <c r="C16" s="14">
+        <f>D2+0.5*$P$2</f>
+        <v>670.71</v>
+      </c>
+      <c r="D16" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B17" s="13">
+        <v>2035</v>
+      </c>
+      <c r="C17" s="14">
+        <f>E2+0.5*$P$2</f>
+        <v>800.71</v>
+      </c>
+      <c r="D17" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B18" s="16">
+        <v>2040</v>
+      </c>
+      <c r="C18" s="17">
+        <f>F2+0.5*$P$2</f>
+        <v>860.71</v>
+      </c>
+      <c r="D18" s="18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="2:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="B21" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="8">
+        <v>967.65</v>
+      </c>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B22" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B23" s="13">
+        <v>2025</v>
+      </c>
+      <c r="C23" s="14">
+        <f>C3+0.5*$P$2</f>
+        <v>319.7</v>
+      </c>
+      <c r="D23" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B24" s="13">
+        <v>2030</v>
+      </c>
+      <c r="C24" s="14">
+        <f>D3+0.5*$P$2</f>
+        <v>328.71</v>
+      </c>
+      <c r="D24" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B25" s="13">
+        <v>2035</v>
+      </c>
+      <c r="C25" s="14">
+        <f>E3+0.5*$P$2</f>
+        <v>405.71</v>
+      </c>
+      <c r="D25" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B26" s="16">
+        <v>2040</v>
+      </c>
+      <c r="C26" s="17">
+        <f>F3+0.5*$P$2</f>
+        <v>510.71</v>
+      </c>
+      <c r="D26" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="2:22" ht="29" x14ac:dyDescent="0.35">
+      <c r="B29" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="8">
+        <v>561.07000000000005</v>
+      </c>
+      <c r="D29" s="9"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B30" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B31" s="13">
+        <v>2025</v>
+      </c>
+      <c r="C31" s="14">
+        <f>C4+0.5*$P$2</f>
+        <v>298.97999999999996</v>
+      </c>
+      <c r="D31" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="B32" s="13">
+        <v>2030</v>
+      </c>
+      <c r="C32" s="14">
+        <f>D4+0.5*$P$2</f>
+        <v>330.71</v>
+      </c>
+      <c r="D32" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B33" s="13">
+        <v>2035</v>
+      </c>
+      <c r="C33" s="14">
+        <f>E4+0.5*$P$2</f>
+        <v>355.71</v>
+      </c>
+      <c r="D33" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B34" s="16">
+        <v>2040</v>
+      </c>
+      <c r="C34" s="17">
+        <f>F4+0.5*$P$2</f>
+        <v>375.71</v>
+      </c>
+      <c r="D34" s="18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+    </row>
+    <row r="37" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B37" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="8">
+        <v>534.14</v>
+      </c>
+      <c r="D37" s="9"/>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B38" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="N7">
-        <v>0.5</v>
-      </c>
-      <c r="O7">
-        <v>0.5</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>1E-3</v>
-      </c>
-      <c r="R7">
-        <v>350</v>
-      </c>
-      <c r="S7">
-        <v>350</v>
-      </c>
-      <c r="T7">
-        <v>350</v>
-      </c>
-      <c r="U7">
-        <v>350</v>
-      </c>
-      <c r="V7">
-        <v>60.209000000000003</v>
-      </c>
-      <c r="W7">
-        <v>32.856999999999999</v>
-      </c>
-      <c r="X7">
-        <v>15.333</v>
-      </c>
-      <c r="Y7">
-        <v>7.6669999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>293</v>
-      </c>
-      <c r="C8">
-        <v>27.61</v>
-      </c>
-      <c r="D8">
-        <v>90.56</v>
-      </c>
-      <c r="E8">
-        <v>130</v>
-      </c>
-      <c r="F8">
-        <v>180</v>
-      </c>
-      <c r="G8">
-        <v>353.38</v>
-      </c>
-      <c r="H8">
-        <v>528.99553595214104</v>
-      </c>
-      <c r="I8">
-        <v>10.4256941812296</v>
-      </c>
-      <c r="J8">
-        <v>22.5</v>
-      </c>
-      <c r="K8">
-        <v>9</v>
-      </c>
-      <c r="L8" t="s">
-        <v>52</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-      <c r="N8">
-        <v>0.5</v>
-      </c>
-      <c r="O8">
-        <v>0.5</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>1E-3</v>
-      </c>
-      <c r="R8">
-        <v>400</v>
-      </c>
-      <c r="S8">
-        <v>400</v>
-      </c>
-      <c r="T8">
-        <v>400</v>
-      </c>
-      <c r="U8">
-        <v>400</v>
-      </c>
-      <c r="V8">
-        <v>8.3089999999999993</v>
-      </c>
-      <c r="W8">
-        <v>5.6</v>
-      </c>
-      <c r="X8">
-        <v>3.1110000000000002</v>
-      </c>
-      <c r="Y8">
-        <v>2.1539999999999999</v>
+      <c r="C38" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="13">
+        <v>2025</v>
+      </c>
+      <c r="C39" s="14">
+        <f>C5+0.5*$P$2</f>
+        <v>309.78999999999996</v>
+      </c>
+      <c r="D39" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="13">
+        <v>2030</v>
+      </c>
+      <c r="C40" s="14">
+        <f>D5+0.5*$P$2</f>
+        <v>550.71</v>
+      </c>
+      <c r="D40" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="13">
+        <v>2035</v>
+      </c>
+      <c r="C41" s="14">
+        <f>E5+0.5*$P$2</f>
+        <v>635.71</v>
+      </c>
+      <c r="D41" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="16">
+        <v>2040</v>
+      </c>
+      <c r="C42" s="17">
+        <f>F5+0.5*$P$2</f>
+        <v>720.71</v>
+      </c>
+      <c r="D42" s="18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="45" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B45" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1135.5999999999999</v>
+      </c>
+      <c r="D45" s="9"/>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B46" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B47" s="13">
+        <v>2025</v>
+      </c>
+      <c r="C47" s="14">
+        <f>C6+0.5*$P$2</f>
+        <v>278.90999999999997</v>
+      </c>
+      <c r="D47" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B48" s="13">
+        <v>2030</v>
+      </c>
+      <c r="C48" s="14">
+        <f>D6+0.5*$P$2</f>
+        <v>293.70999999999998</v>
+      </c>
+      <c r="D48" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B49" s="13">
+        <v>2035</v>
+      </c>
+      <c r="C49" s="14">
+        <f>E6+0.5*$P$2</f>
+        <v>322.70999999999998</v>
+      </c>
+      <c r="D49" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B50" s="16">
+        <v>2040</v>
+      </c>
+      <c r="C50" s="17">
+        <f>F6+0.5*$P$2</f>
+        <v>350.71</v>
+      </c>
+      <c r="D50" s="18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+    </row>
+    <row r="53" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B53" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="8">
+        <v>969.52</v>
+      </c>
+      <c r="D53" s="9"/>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B54" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B55" s="13">
+        <v>2025</v>
+      </c>
+      <c r="C55" s="14">
+        <f>C7+0.5*$P$2</f>
+        <v>288.32</v>
+      </c>
+      <c r="D55" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B56" s="13">
+        <v>2030</v>
+      </c>
+      <c r="C56" s="14">
+        <f>D7+0.5*$P$2</f>
+        <v>351.27</v>
+      </c>
+      <c r="D56" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B57" s="13">
+        <v>2035</v>
+      </c>
+      <c r="C57" s="14">
+        <f>E7+0.5*$P$2</f>
+        <v>390.71</v>
+      </c>
+      <c r="D57" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B58" s="16">
+        <v>2040</v>
+      </c>
+      <c r="C58" s="17">
+        <f>F7+0.5*$P$2</f>
+        <v>440.71</v>
+      </c>
+      <c r="D58" s="18">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1416,19 +1908,16 @@
         <v>11.132999999999999</v>
       </c>
       <c r="E2">
-        <v>17.6388854019112</v>
+        <v>13.78042157888167</v>
       </c>
       <c r="F2">
-        <v>9.82</v>
+        <v>10.5</v>
       </c>
       <c r="G2">
-        <v>10.5</v>
-      </c>
-      <c r="H2">
         <v>14.59645230960589</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1442,19 +1931,16 @@
         <v>18.760000000000002</v>
       </c>
       <c r="E3">
-        <v>21.334694335229148</v>
+        <v>18.133640203215091</v>
       </c>
       <c r="F3">
-        <v>14.848000000000001</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="G3">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="H3">
         <v>8.4362881656626847</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1468,119 +1954,81 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>16.257160261596411</v>
+        <v>14.737656155323689</v>
       </c>
       <c r="F4">
-        <v>13.178000000000001</v>
+        <v>14.2</v>
       </c>
       <c r="G4">
-        <v>14.2</v>
-      </c>
-      <c r="H4">
         <v>14.449824965889</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
       <c r="B5">
-        <v>12.40564545454545</v>
+        <v>13.232892950285249</v>
       </c>
       <c r="C5">
-        <v>17.728781818181819</v>
+        <v>16.307173512632438</v>
       </c>
       <c r="D5">
-        <v>14.228463636363641</v>
+        <v>13.710080806845969</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>42.834790909090913</v>
+        <v>13.172616136919309</v>
       </c>
       <c r="G5">
-        <v>11.1</v>
-      </c>
-      <c r="H5">
-        <v>19.043804912696341</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18.882414716557939</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
       <c r="B6">
-        <v>14.082000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>14.848000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="D6">
-        <v>13.178000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="E6">
-        <v>19.422772091608628</v>
+        <v>7.024572127139364</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>15.3</v>
-      </c>
-      <c r="H6">
-        <v>18.716759874443969</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>4.5</v>
+        <v>14.122395904436861</v>
       </c>
       <c r="C7">
-        <v>6.2</v>
+        <v>8.123641638225255</v>
       </c>
       <c r="D7">
-        <v>8.5</v>
+        <v>13.78744368600683</v>
       </c>
       <c r="E7">
-        <v>5.0999999999999996</v>
+        <v>19.752714320654551</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>14.122395904436861</v>
-      </c>
-      <c r="C8">
-        <v>8.123641638225255</v>
-      </c>
-      <c r="D8">
-        <v>13.78744368600683</v>
-      </c>
-      <c r="E8">
-        <v>20.700736057116242</v>
-      </c>
-      <c r="F8">
-        <v>18.779641638225261</v>
-      </c>
-      <c r="G8">
-        <v>12.5</v>
-      </c>
-      <c r="H8">
         <v>0</v>
       </c>
     </row>
@@ -1592,16 +2040,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/input_data_intertemporal_final.xlsx
+++ b/inputs/input_data_intertemporal_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EEG\EPEC\EPEC_VS_code\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF84FCA-830E-43AF-B02A-5EA1FEFBD53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2824C566-B7DE-4AC5-81E8-EF0E9335B1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-930" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6300" yWindow="1890" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -378,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -410,16 +410,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -436,7 +433,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -739,9 +736,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -749,12 +746,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -762,37 +759,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -805,9 +802,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -815,7 +812,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -823,7 +820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -831,7 +828,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -839,7 +836,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -847,7 +844,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -855,7 +852,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -871,33 +868,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:W58"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.7265625" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="15.453125" customWidth="1"/>
-    <col min="6" max="6" width="15.7265625" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" customWidth="1"/>
-    <col min="8" max="8" width="24.90625" customWidth="1"/>
-    <col min="9" max="9" width="20.54296875" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="8" max="8" width="24.85546875" customWidth="1"/>
+    <col min="9" max="9" width="20.5703125" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="18.36328125" customWidth="1"/>
-    <col min="12" max="12" width="17.1796875" customWidth="1"/>
-    <col min="13" max="13" width="17.54296875" customWidth="1"/>
-    <col min="14" max="14" width="20.26953125" customWidth="1"/>
-    <col min="15" max="15" width="22.1796875" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="17.140625" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" customWidth="1"/>
+    <col min="14" max="14" width="20.28515625" customWidth="1"/>
+    <col min="15" max="15" width="22.140625" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="15.7265625" customWidth="1"/>
+    <col min="18" max="18" width="15.7109375" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
-    <col min="20" max="20" width="17.26953125" customWidth="1"/>
-    <col min="21" max="21" width="16.81640625" customWidth="1"/>
-    <col min="22" max="22" width="17.7265625" customWidth="1"/>
-    <col min="23" max="23" width="20.81640625" customWidth="1"/>
+    <col min="20" max="20" width="17.28515625" customWidth="1"/>
+    <col min="21" max="21" width="16.85546875" customWidth="1"/>
+    <col min="22" max="22" width="17.7109375" customWidth="1"/>
+    <col min="23" max="23" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -968,7 +965,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1039,7 +1036,7 @@
         <v>0.309</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1110,7 +1107,7 @@
         <v>0.74099999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1181,7 +1178,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1252,7 +1249,7 @@
         <v>0.40235724482512492</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1323,7 +1320,7 @@
         <v>2.0579999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1394,157 +1391,191 @@
         <v>1.026</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
     </row>
-    <row r="13" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="7" t="s">
+    <row r="13" spans="1:23" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="F13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="8">
+      <c r="G13" s="8">
         <v>521.41999999999996</v>
       </c>
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="B14" s="10" t="s">
+      <c r="H13" s="9"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="F14" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="G14" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="H14" s="12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="B15" s="13">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B15" s="13"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="14"/>
+      <c r="F15" s="13">
         <v>2025</v>
       </c>
-      <c r="C15" s="14">
-        <f>C2+0.5*$P$2</f>
+      <c r="G15" s="4">
         <v>538.71</v>
       </c>
-      <c r="D15" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="B16" s="13">
+      <c r="H15" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B16" s="13"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="14"/>
+      <c r="F16" s="13">
         <v>2030</v>
       </c>
-      <c r="C16" s="14">
-        <f>D2+0.5*$P$2</f>
+      <c r="G16" s="4">
         <v>670.71</v>
       </c>
-      <c r="D16" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B17" s="13">
+      <c r="H16" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B17" s="13"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="14"/>
+      <c r="F17" s="13">
         <v>2035</v>
       </c>
-      <c r="C17" s="14">
-        <f>E2+0.5*$P$2</f>
+      <c r="G17" s="4">
         <v>800.71</v>
       </c>
-      <c r="D17" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B18" s="16">
+      <c r="H17" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="F18" s="15">
         <v>2040</v>
       </c>
-      <c r="C18" s="17">
-        <f>F2+0.5*$P$2</f>
+      <c r="G18" s="16">
         <v>860.71</v>
       </c>
-      <c r="D18" s="18">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="H18" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="2:22" ht="29" x14ac:dyDescent="0.35">
-      <c r="B21" s="7" t="s">
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="B21" s="7"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="9"/>
+      <c r="F21" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="8">
+      <c r="G21" s="8">
         <v>967.65</v>
       </c>
-      <c r="D21" s="9"/>
-    </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B22" s="10" t="s">
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="12"/>
+      <c r="F22" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="G22" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="H22" s="12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B23" s="13">
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B23" s="13"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="14"/>
+      <c r="F23" s="13">
         <v>2025</v>
       </c>
-      <c r="C23" s="14">
-        <f>C3+0.5*$P$2</f>
+      <c r="G23" s="4">
         <v>319.7</v>
       </c>
-      <c r="D23" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B24" s="13">
+      <c r="H23" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B24" s="13"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="14"/>
+      <c r="F24" s="13">
         <v>2030</v>
       </c>
-      <c r="C24" s="14">
-        <f>D3+0.5*$P$2</f>
+      <c r="G24" s="4">
         <v>328.71</v>
       </c>
-      <c r="D24" s="15">
+      <c r="H24" s="14">
         <v>0.5</v>
       </c>
       <c r="R24" s="3"/>
     </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B25" s="13">
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B25" s="13"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="14"/>
+      <c r="F25" s="13">
         <v>2035</v>
       </c>
-      <c r="C25" s="14">
-        <f>E3+0.5*$P$2</f>
+      <c r="G25" s="4">
         <v>405.71</v>
       </c>
-      <c r="D25" s="15">
+      <c r="H25" s="14">
         <v>0.5</v>
       </c>
       <c r="R25" s="3"/>
     </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B26" s="16">
+    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B26" s="15"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="F26" s="15">
         <v>2040</v>
       </c>
-      <c r="C26" s="17">
-        <f>F3+0.5*$P$2</f>
+      <c r="G26" s="16">
         <v>510.71</v>
       </c>
-      <c r="D26" s="18">
+      <c r="H26" s="17">
         <v>0.5</v>
       </c>
       <c r="R26" s="3"/>
@@ -1553,310 +1584,387 @@
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
     </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.35">
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
-    </row>
-    <row r="29" spans="2:22" ht="29" x14ac:dyDescent="0.35">
-      <c r="B29" s="7" t="s">
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="B29" s="7"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="9"/>
+      <c r="F29" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="8">
+      <c r="G29" s="8">
         <v>561.07000000000005</v>
       </c>
-      <c r="D29" s="9"/>
-    </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B30" s="10" t="s">
+      <c r="H29" s="9"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="12"/>
+      <c r="F30" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="G30" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="H30" s="12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B31" s="13">
+    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B31" s="13"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="14"/>
+      <c r="F31" s="13">
         <v>2025</v>
       </c>
-      <c r="C31" s="14">
-        <f>C4+0.5*$P$2</f>
+      <c r="G31" s="4">
         <v>298.97999999999996</v>
       </c>
-      <c r="D31" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.35">
-      <c r="B32" s="13">
+      <c r="H31" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B32" s="13"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="14"/>
+      <c r="F32" s="13">
         <v>2030</v>
       </c>
-      <c r="C32" s="14">
-        <f>D4+0.5*$P$2</f>
+      <c r="G32" s="4">
         <v>330.71</v>
       </c>
-      <c r="D32" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B33" s="13">
+      <c r="H32" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="13"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="14"/>
+      <c r="F33" s="13">
         <v>2035</v>
       </c>
-      <c r="C33" s="14">
-        <f>E4+0.5*$P$2</f>
+      <c r="G33" s="4">
         <v>355.71</v>
       </c>
-      <c r="D33" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B34" s="16">
+      <c r="H33" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="15"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
+      <c r="F34" s="15">
         <v>2040</v>
       </c>
-      <c r="C34" s="17">
-        <f>F4+0.5*$P$2</f>
+      <c r="G34" s="16">
         <v>375.71</v>
       </c>
-      <c r="D34" s="18">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="H34" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
-    </row>
-    <row r="37" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B37" s="7" t="s">
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="B37" s="7"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="9"/>
+      <c r="F37" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="8">
+      <c r="G37" s="8">
         <v>534.14</v>
       </c>
-      <c r="D37" s="9"/>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B38" s="10" t="s">
+      <c r="H37" s="9"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="10"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="12"/>
+      <c r="F38" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="G38" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="H38" s="12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B39" s="13">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="13"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="14"/>
+      <c r="F39" s="13">
         <v>2025</v>
       </c>
-      <c r="C39" s="14">
-        <f>C5+0.5*$P$2</f>
+      <c r="G39" s="4">
         <v>309.78999999999996</v>
       </c>
-      <c r="D39" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B40" s="13">
+      <c r="H39" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="13"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="14"/>
+      <c r="F40" s="13">
         <v>2030</v>
       </c>
-      <c r="C40" s="14">
-        <f>D5+0.5*$P$2</f>
+      <c r="G40" s="4">
         <v>550.71</v>
       </c>
-      <c r="D40" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B41" s="13">
+      <c r="H40" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="13"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="14"/>
+      <c r="F41" s="13">
         <v>2035</v>
       </c>
-      <c r="C41" s="14">
-        <f>E5+0.5*$P$2</f>
+      <c r="G41" s="4">
         <v>635.71</v>
       </c>
-      <c r="D41" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B42" s="16">
+      <c r="H41" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="15"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
+      <c r="F42" s="15">
         <v>2040</v>
       </c>
-      <c r="C42" s="17">
-        <f>F5+0.5*$P$2</f>
+      <c r="G42" s="16">
         <v>720.71</v>
       </c>
-      <c r="D42" s="18">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="H42" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
-    </row>
-    <row r="45" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B45" s="7" t="s">
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="45" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="B45" s="7"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="9"/>
+      <c r="F45" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C45" s="8">
+      <c r="G45" s="8">
         <v>1135.5999999999999</v>
       </c>
-      <c r="D45" s="9"/>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B46" s="10" t="s">
+      <c r="H45" s="9"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B46" s="10"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="12"/>
+      <c r="F46" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="G46" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="H46" s="12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B47" s="13">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="13"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="14"/>
+      <c r="F47" s="13">
         <v>2025</v>
       </c>
-      <c r="C47" s="14">
-        <f>C6+0.5*$P$2</f>
+      <c r="G47" s="4">
         <v>278.90999999999997</v>
       </c>
-      <c r="D47" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B48" s="13">
+      <c r="H47" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="13"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="14"/>
+      <c r="F48" s="13">
         <v>2030</v>
       </c>
-      <c r="C48" s="14">
-        <f>D6+0.5*$P$2</f>
+      <c r="G48" s="4">
         <v>293.70999999999998</v>
       </c>
-      <c r="D48" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B49" s="13">
+      <c r="H48" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49" s="13"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="14"/>
+      <c r="F49" s="13">
         <v>2035</v>
       </c>
-      <c r="C49" s="14">
-        <f>E6+0.5*$P$2</f>
+      <c r="G49" s="4">
         <v>322.70999999999998</v>
       </c>
-      <c r="D49" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B50" s="16">
+      <c r="H49" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="15"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
+      <c r="F50" s="15">
         <v>2040</v>
       </c>
-      <c r="C50" s="17">
-        <f>F6+0.5*$P$2</f>
+      <c r="G50" s="16">
         <v>350.71</v>
       </c>
-      <c r="D50" s="18">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="H50" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
-    </row>
-    <row r="53" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B53" s="7" t="s">
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="B53" s="7"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="9"/>
+      <c r="F53" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C53" s="8">
+      <c r="G53" s="8">
         <v>969.52</v>
       </c>
-      <c r="D53" s="9"/>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B54" s="10" t="s">
+      <c r="H53" s="9"/>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54" s="10"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="12"/>
+      <c r="F54" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="G54" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="H54" s="12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B55" s="13">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55" s="13"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="14"/>
+      <c r="F55" s="13">
         <v>2025</v>
       </c>
-      <c r="C55" s="14">
-        <f>C7+0.5*$P$2</f>
+      <c r="G55" s="4">
         <v>288.32</v>
       </c>
-      <c r="D55" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B56" s="13">
+      <c r="H55" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56" s="13"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="14"/>
+      <c r="F56" s="13">
         <v>2030</v>
       </c>
-      <c r="C56" s="14">
-        <f>D7+0.5*$P$2</f>
+      <c r="G56" s="4">
         <v>351.27</v>
       </c>
-      <c r="D56" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B57" s="13">
+      <c r="H56" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57" s="13"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="14"/>
+      <c r="F57" s="13">
         <v>2035</v>
       </c>
-      <c r="C57" s="14">
-        <f>E7+0.5*$P$2</f>
+      <c r="G57" s="4">
         <v>390.71</v>
       </c>
-      <c r="D57" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B58" s="16">
+      <c r="H57" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B58" s="15"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
+      <c r="F58" s="15">
         <v>2040</v>
       </c>
-      <c r="C58" s="17">
-        <f>F7+0.5*$P$2</f>
+      <c r="G58" s="16">
         <v>440.71</v>
       </c>
-      <c r="D58" s="18">
+      <c r="H58" s="17">
         <v>0.5</v>
       </c>
     </row>
@@ -1869,9 +1977,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -1894,7 +2002,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1917,7 +2025,7 @@
         <v>14.59645230960589</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1940,7 +2048,7 @@
         <v>8.4362881656626847</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1963,7 +2071,7 @@
         <v>14.449824965889</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1986,7 +2094,7 @@
         <v>18.882414716557939</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2009,7 +2117,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -2040,14 +2148,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>

--- a/inputs/input_data_intertemporal_final.xlsx
+++ b/inputs/input_data_intertemporal_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alexander\Studium\EEG\Complementarity Modelling\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EEG\EPEC\EPEC_VS_code\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2824C566-B7DE-4AC5-81E8-EF0E9335B1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD958E1-5271-4DCC-B382-49BF469CD300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6300" yWindow="1890" windowWidth="31530" windowHeight="16905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -736,9 +736,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,12 +746,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -759,37 +759,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -802,9 +802,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -812,7 +812,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -820,7 +820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -828,7 +828,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -836,7 +836,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -844,7 +844,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -852,7 +852,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -868,33 +868,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:W58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7265625" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="24.85546875" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" customWidth="1"/>
+    <col min="8" max="8" width="24.81640625" customWidth="1"/>
+    <col min="9" max="9" width="20.54296875" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" customWidth="1"/>
-    <col min="12" max="12" width="17.140625" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" customWidth="1"/>
-    <col min="14" max="14" width="20.28515625" customWidth="1"/>
-    <col min="15" max="15" width="22.140625" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" customWidth="1"/>
+    <col min="12" max="12" width="17.1796875" customWidth="1"/>
+    <col min="13" max="13" width="17.54296875" customWidth="1"/>
+    <col min="14" max="14" width="20.26953125" customWidth="1"/>
+    <col min="15" max="15" width="22.1796875" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="15.7109375" customWidth="1"/>
+    <col min="18" max="18" width="15.7265625" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
-    <col min="20" max="20" width="17.28515625" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" customWidth="1"/>
-    <col min="22" max="22" width="17.7109375" customWidth="1"/>
-    <col min="23" max="23" width="20.85546875" customWidth="1"/>
+    <col min="20" max="20" width="17.26953125" customWidth="1"/>
+    <col min="21" max="21" width="16.81640625" customWidth="1"/>
+    <col min="22" max="22" width="17.7265625" customWidth="1"/>
+    <col min="23" max="23" width="20.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -965,7 +965,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>0.309</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>0.74099999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>0.40235724482512492</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>2.0579999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1391,13 +1391,13 @@
         <v>1.026</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
     </row>
-    <row r="13" spans="1:23" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="7"/>
       <c r="C13" s="8"/>
       <c r="D13" s="9"/>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
       <c r="D14" s="12"/>
@@ -1423,7 +1423,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="B15" s="13"/>
       <c r="C15" s="4"/>
       <c r="D15" s="14"/>
@@ -1437,7 +1437,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="B16" s="13"/>
       <c r="C16" s="4"/>
       <c r="D16" s="14"/>
@@ -1451,7 +1451,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B17" s="13"/>
       <c r="C17" s="4"/>
       <c r="D17" s="14"/>
@@ -1465,7 +1465,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B18" s="15"/>
       <c r="C18" s="16"/>
       <c r="D18" s="17"/>
@@ -1479,7 +1479,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -1487,7 +1487,7 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -1495,7 +1495,7 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:22" ht="29" x14ac:dyDescent="0.35">
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
       <c r="D21" s="9"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B22" s="10"/>
       <c r="C22" s="11"/>
       <c r="D22" s="12"/>
@@ -1521,7 +1521,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B23" s="13"/>
       <c r="C23" s="4"/>
       <c r="D23" s="14"/>
@@ -1535,7 +1535,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B24" s="13"/>
       <c r="C24" s="4"/>
       <c r="D24" s="14"/>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="R24" s="3"/>
     </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B25" s="13"/>
       <c r="C25" s="4"/>
       <c r="D25" s="14"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="R25" s="3"/>
     </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B26" s="15"/>
       <c r="C26" s="16"/>
       <c r="D26" s="17"/>
@@ -1584,7 +1584,7 @@
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
     </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -1592,7 +1592,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -1600,7 +1600,7 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:22" ht="29" x14ac:dyDescent="0.35">
       <c r="B29" s="7"/>
       <c r="C29" s="8"/>
       <c r="D29" s="9"/>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B30" s="10"/>
       <c r="C30" s="11"/>
       <c r="D30" s="12"/>
@@ -1626,7 +1626,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B31" s="13"/>
       <c r="C31" s="4"/>
       <c r="D31" s="14"/>
@@ -1640,7 +1640,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B32" s="13"/>
       <c r="C32" s="4"/>
       <c r="D32" s="14"/>
@@ -1654,7 +1654,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B33" s="13"/>
       <c r="C33" s="4"/>
       <c r="D33" s="14"/>
@@ -1668,7 +1668,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B34" s="15"/>
       <c r="C34" s="16"/>
       <c r="D34" s="17"/>
@@ -1682,7 +1682,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -1690,7 +1690,7 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -1698,7 +1698,7 @@
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" ht="29" x14ac:dyDescent="0.35">
       <c r="B37" s="7"/>
       <c r="C37" s="8"/>
       <c r="D37" s="9"/>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H37" s="9"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B38" s="10"/>
       <c r="C38" s="11"/>
       <c r="D38" s="12"/>
@@ -1724,7 +1724,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B39" s="13"/>
       <c r="C39" s="4"/>
       <c r="D39" s="14"/>
@@ -1738,7 +1738,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B40" s="13"/>
       <c r="C40" s="4"/>
       <c r="D40" s="14"/>
@@ -1752,7 +1752,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B41" s="13"/>
       <c r="C41" s="4"/>
       <c r="D41" s="14"/>
@@ -1766,7 +1766,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B42" s="15"/>
       <c r="C42" s="16"/>
       <c r="D42" s="17"/>
@@ -1780,7 +1780,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -1788,7 +1788,7 @@
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
-    <row r="45" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:8" ht="29" x14ac:dyDescent="0.35">
       <c r="B45" s="7"/>
       <c r="C45" s="8"/>
       <c r="D45" s="9"/>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="H45" s="9"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
       <c r="D46" s="12"/>
@@ -1814,7 +1814,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B47" s="13"/>
       <c r="C47" s="4"/>
       <c r="D47" s="14"/>
@@ -1828,7 +1828,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B48" s="13"/>
       <c r="C48" s="4"/>
       <c r="D48" s="14"/>
@@ -1842,7 +1842,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B49" s="13"/>
       <c r="C49" s="4"/>
       <c r="D49" s="14"/>
@@ -1856,7 +1856,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B50" s="15"/>
       <c r="C50" s="16"/>
       <c r="D50" s="17"/>
@@ -1870,7 +1870,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -1878,7 +1878,7 @@
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -1886,7 +1886,7 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:8" ht="29" x14ac:dyDescent="0.35">
       <c r="B53" s="7"/>
       <c r="C53" s="8"/>
       <c r="D53" s="9"/>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="H53" s="9"/>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
       <c r="D54" s="12"/>
@@ -1912,7 +1912,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B55" s="13"/>
       <c r="C55" s="4"/>
       <c r="D55" s="14"/>
@@ -1926,7 +1926,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B56" s="13"/>
       <c r="C56" s="4"/>
       <c r="D56" s="14"/>
@@ -1940,7 +1940,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B57" s="13"/>
       <c r="C57" s="4"/>
       <c r="D57" s="14"/>
@@ -1954,7 +1954,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B58" s="15"/>
       <c r="C58" s="16"/>
       <c r="D58" s="17"/>
@@ -1977,9 +1977,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>14.59645230960589</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>8.4362881656626847</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>14.449824965889</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>18.882414716557939</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -2148,14 +2148,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>52</v>
       </c>

--- a/inputs/input_data_intertemporal_final.xlsx
+++ b/inputs/input_data_intertemporal_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EEG\EPEC\EPEC_VS_code\SolarGeoRisk_EPEC_intertemporal\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD958E1-5271-4DCC-B382-49BF469CD300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAEB294-82EF-4A28-861A-B484C2E7927B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-930" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -204,9 +204,6 @@
 </t>
   </si>
   <si>
-    <t>q</t>
-  </si>
-  <si>
     <t>k</t>
   </si>
   <si>
@@ -214,6 +211,9 @@
   </si>
   <si>
     <t>estimated WTP for full demand</t>
+  </si>
+  <si>
+    <t>interceptor</t>
   </si>
 </sst>
 </file>
@@ -378,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -430,6 +430,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1402,7 +1405,7 @@
       <c r="C13" s="8"/>
       <c r="D13" s="9"/>
       <c r="F13" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13" s="8">
         <v>521.41999999999996</v>
@@ -1414,14 +1417,17 @@
       <c r="C14" s="11"/>
       <c r="D14" s="12"/>
       <c r="F14" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>54</v>
-      </c>
+      <c r="J14" s="18"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="B15" s="13"/>
@@ -1436,6 +1442,9 @@
       <c r="H15" s="14">
         <v>0.5</v>
       </c>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="B16" s="13"/>
@@ -1450,6 +1459,9 @@
       <c r="H16" s="14">
         <v>0.5</v>
       </c>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B17" s="13"/>
@@ -1464,6 +1476,9 @@
       <c r="H17" s="14">
         <v>0.5</v>
       </c>
+      <c r="J17" s="4"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B18" s="15"/>
@@ -1500,7 +1515,7 @@
       <c r="C21" s="8"/>
       <c r="D21" s="9"/>
       <c r="F21" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G21" s="8">
         <v>967.65</v>
@@ -1515,10 +1530,10 @@
         <v>16</v>
       </c>
       <c r="G22" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.35">
@@ -1605,7 +1620,7 @@
       <c r="C29" s="8"/>
       <c r="D29" s="9"/>
       <c r="F29" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G29" s="8">
         <v>561.07000000000005</v>
@@ -1620,10 +1635,10 @@
         <v>18</v>
       </c>
       <c r="G30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.35">
@@ -1703,7 +1718,7 @@
       <c r="C37" s="8"/>
       <c r="D37" s="9"/>
       <c r="F37" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G37" s="8">
         <v>534.14</v>
@@ -1718,10 +1733,10 @@
         <v>20</v>
       </c>
       <c r="G38" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H38" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.35">
@@ -1793,7 +1808,7 @@
       <c r="C45" s="8"/>
       <c r="D45" s="9"/>
       <c r="F45" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G45" s="8">
         <v>1135.5999999999999</v>
@@ -1808,10 +1823,10 @@
         <v>22</v>
       </c>
       <c r="G46" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H46" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="H46" s="12" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.35">
@@ -1891,7 +1906,7 @@
       <c r="C53" s="8"/>
       <c r="D53" s="9"/>
       <c r="F53" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G53" s="8">
         <v>969.52</v>
@@ -1906,10 +1921,10 @@
         <v>24</v>
       </c>
       <c r="G54" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H54" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="H54" s="12" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.35">
